--- a/GameConfig/level.xlsx
+++ b/GameConfig/level.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -135,6 +135,12 @@
   <si>
     <t>每一行的作用是固定的不可更改</t>
     <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>level_11003</t>
+  </si>
+  <si>
+    <t>monster_3001;monster_3003;</t>
   </si>
 </sst>
 </file>
@@ -729,7 +735,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15.75" style="3" customWidth="1"/>
@@ -804,9 +810,23 @@
         <v>13</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="B6" s="9" t="s">
+        <v>13</v>
+      </c>
+      <c r="C6" s="9" t="s">
         <v>17</v>
       </c>
-      <c r="D5" s="9" t="s">
+      <c r="D6" s="9" t="s">
         <v>8</v>
       </c>
     </row>

--- a/GameConfig/level.xlsx
+++ b/GameConfig/level.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -34,10 +34,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>level_11001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>level_11002</t>
   </si>
   <si>
@@ -45,15 +41,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>bgm_238001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>bgmId</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm_238002</t>
   </si>
   <si>
     <t>加农炮id</t>
@@ -141,6 +130,20 @@
   </si>
   <si>
     <t>monster_3001;monster_3003;</t>
+  </si>
+  <si>
+    <t>level_11001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_238002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_238003</t>
+  </si>
+  <si>
+    <t>bgm_238004</t>
   </si>
 </sst>
 </file>
@@ -751,13 +754,13 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="C1" s="10" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
@@ -765,13 +768,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C2" s="11" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
@@ -779,10 +782,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C3" s="12" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="D3" s="13" t="s">
         <v>2</v>
@@ -790,44 +793,44 @@
     </row>
     <row r="4" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
-        <v>3</v>
+        <v>22</v>
       </c>
       <c r="B4" s="9" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C4" s="9" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>6</v>
+        <v>23</v>
       </c>
     </row>
     <row r="5" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C5" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="D5" s="9" t="s">
         <v>24</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>8</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
@@ -848,17 +851,17 @@
   <sheetData>
     <row r="1" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="18" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -866,7 +869,7 @@
     </row>
     <row r="5" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/level.xlsx
+++ b/GameConfig/level.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="26">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -45,42 +45,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>加农炮id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cannonId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>string</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cannon_91001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>cannon_91002</t>
-  </si>
-  <si>
-    <t>怪物id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>monsterId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>string[]</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>monster_3001;monster_3002;monster_3003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>monster_3001;monster_3002;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -129,9 +94,6 @@
     <t>level_11003</t>
   </si>
   <si>
-    <t>monster_3001;monster_3003;</t>
-  </si>
-  <si>
     <t>level_11001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -144,6 +106,23 @@
   </si>
   <si>
     <t>bgm_238004</t>
+  </si>
+  <si>
+    <t>炮弹id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bulletId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bullet_89001</t>
+  </si>
+  <si>
+    <t>bullet_89002</t>
+  </si>
+  <si>
+    <t>bullet_89003</t>
   </si>
 </sst>
 </file>
@@ -738,99 +717,80 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:C6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="2" width="15.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="34.75" style="3" customWidth="1"/>
-    <col min="4" max="4" width="27.125" style="3" customWidth="1"/>
-    <col min="5" max="5" width="9" style="1"/>
-    <col min="6" max="6" width="13.75" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="1"/>
+    <col min="3" max="3" width="27.125" style="3" customWidth="1"/>
+    <col min="4" max="4" width="9" style="1"/>
+    <col min="5" max="5" width="13.75" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>6</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>7</v>
-      </c>
-      <c r="C2" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="D2" s="7" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>8</v>
-      </c>
-      <c r="C3" s="12" t="s">
+        <v>6</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>18</v>
+      </c>
+      <c r="C4" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="13" t="s">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="B4" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="9" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>21</v>
-      </c>
-      <c r="D5" s="9" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B6" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="9" t="s">
-        <v>10</v>
-      </c>
       <c r="C6" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>25</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -851,17 +811,17 @@
   <sheetData>
     <row r="1" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="14" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="14" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="18" t="s">
-        <v>18</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
@@ -869,7 +829,7 @@
     </row>
     <row r="5" spans="1:1" ht="28.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="16" t="s">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>

--- a/GameConfig/level.xlsx
+++ b/GameConfig/level.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="21">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
   <si>
     <t>id</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -94,35 +94,57 @@
     <t>level_11003</t>
   </si>
   <si>
+    <t>bgm_238002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bgm_238003</t>
+  </si>
+  <si>
+    <t>bgm_238004</t>
+  </si>
+  <si>
+    <t>炮弹id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bulletId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>bullet_89001</t>
+  </si>
+  <si>
+    <t>bullet_89002</t>
+  </si>
+  <si>
+    <t>bullet_89003</t>
+  </si>
+  <si>
+    <t>block_58001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>block_58002</t>
+  </si>
+  <si>
+    <t>block_58003</t>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>blockId</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>砖块Id</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>level_11001</t>
     <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm_238002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bgm_238003</t>
-  </si>
-  <si>
-    <t>bgm_238004</t>
-  </si>
-  <si>
-    <t>炮弹id</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bulletId</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>bullet_89001</t>
-  </si>
-  <si>
-    <t>bullet_89002</t>
-  </si>
-  <si>
-    <t>bullet_89003</t>
   </si>
 </sst>
 </file>
@@ -207,7 +229,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="12">
+  <borders count="15">
     <border>
       <left/>
       <right/>
@@ -376,11 +398,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color theme="0"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color theme="0"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color theme="0"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -435,6 +496,15 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="3" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -717,80 +787,98 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:C6"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="15.75" style="3" customWidth="1"/>
-    <col min="3" max="3" width="27.125" style="3" customWidth="1"/>
-    <col min="4" max="4" width="9" style="1"/>
-    <col min="5" max="5" width="13.75" style="1" customWidth="1"/>
-    <col min="6" max="16384" width="9" style="1"/>
+    <col min="1" max="3" width="15.75" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.125" style="3" customWidth="1"/>
+    <col min="5" max="5" width="9" style="1"/>
+    <col min="6" max="6" width="13.75" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>16</v>
-      </c>
-      <c r="C1" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="C1" s="20" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="5" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="6" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="C2" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" s="21" t="s">
+        <v>24</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="8" t="s">
         <v>2</v>
       </c>
       <c r="B3" s="12" t="s">
         <v>6</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="D3" s="13" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B4" s="9" t="s">
+        <v>17</v>
+      </c>
+      <c r="C4" s="9" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="9" t="s">
-        <v>18</v>
-      </c>
-      <c r="C4" s="9" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+    </row>
+    <row r="5" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>3</v>
       </c>
       <c r="B5" s="9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" s="9" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
+        <v>21</v>
+      </c>
+      <c r="D5" s="9" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="13.15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>15</v>
+        <v>22</v>
+      </c>
+      <c r="D6" s="9" t="s">
+        <v>14</v>
       </c>
     </row>
   </sheetData>
